--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.72760740150689</v>
+        <v>8.73073620274487</v>
       </c>
       <c r="D2" t="n">
-        <v>53.72912085858614</v>
+        <v>8.730982139520247</v>
       </c>
       <c r="E2" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F2" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.61558371914611</v>
+        <v>7.250032354361243</v>
       </c>
       <c r="D3" t="n">
-        <v>44.57291836707221</v>
+        <v>7.243099234649233</v>
       </c>
       <c r="E3" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F3" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.19253993492251</v>
+        <v>6.856287739424909</v>
       </c>
       <c r="D4" t="n">
-        <v>42.10869580199777</v>
+        <v>6.842663067824637</v>
       </c>
       <c r="E4" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F4" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.27718838331988</v>
+        <v>4.59504311228948</v>
       </c>
       <c r="D5" t="n">
-        <v>28.32771784522804</v>
+        <v>4.603254149849556</v>
       </c>
       <c r="E5" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F5" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.943898732454305</v>
+        <v>1.290883544023825</v>
       </c>
       <c r="D6" t="n">
-        <v>7.833029568711439</v>
+        <v>1.272867304915609</v>
       </c>
       <c r="E6" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F6" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.61953790904279</v>
+        <v>4.000674910219453</v>
       </c>
       <c r="D7" t="n">
-        <v>24.57107798202008</v>
+        <v>3.992800172078263</v>
       </c>
       <c r="E7" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F7" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>51.12008519512473</v>
+        <v>8.307013844207768</v>
       </c>
       <c r="D8" t="n">
-        <v>51.15518731279615</v>
+        <v>8.312717938329374</v>
       </c>
       <c r="E8" t="n">
-        <v>15.26774013334989</v>
+        <v>2.481007771669357</v>
       </c>
       <c r="F8" t="n">
-        <v>15.29548137312987</v>
+        <v>2.485515723133604</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
